--- a/data/CHI_SO_PHAI_SINH.xlsx
+++ b/data/CHI_SO_PHAI_SINH.xlsx
@@ -255,12 +255,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ba Đình'!$A$2:$A$15</f>
+              <f>'Ba Đình'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ba Đình'!$B$2:$B$15</f>
+              <f>'Ba Đình'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -290,12 +290,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ba Đình'!$A$2:$A$15</f>
+              <f>'Ba Đình'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ba Đình'!$C$2:$C$15</f>
+              <f>'Ba Đình'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -330,7 +330,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Ba Đình'!$D$2:$D$15</f>
+              <f>'Ba Đình'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -360,7 +360,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Ba Đình'!$E$2:$E$15</f>
+              <f>'Ba Đình'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Nam Từ Liêm'!$A$2:$A$15</f>
+              <f>'Nam Từ Liêm'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Nam Từ Liêm'!$B$2:$B$15</f>
+              <f>'Nam Từ Liêm'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -539,12 +539,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Nam Từ Liêm'!$A$2:$A$15</f>
+              <f>'Nam Từ Liêm'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Nam Từ Liêm'!$C$2:$C$15</f>
+              <f>'Nam Từ Liêm'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -579,7 +579,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Nam Từ Liêm'!$D$2:$D$15</f>
+              <f>'Nam Từ Liêm'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -609,7 +609,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Nam Từ Liêm'!$E$2:$E$15</f>
+              <f>'Nam Từ Liêm'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -753,12 +753,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Thanh Trì'!$A$2:$A$15</f>
+              <f>'Thanh Trì'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Thanh Trì'!$B$2:$B$15</f>
+              <f>'Thanh Trì'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -788,12 +788,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Thanh Trì'!$A$2:$A$15</f>
+              <f>'Thanh Trì'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Thanh Trì'!$C$2:$C$15</f>
+              <f>'Thanh Trì'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -828,7 +828,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Thanh Trì'!$D$2:$D$15</f>
+              <f>'Thanh Trì'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -858,7 +858,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Thanh Trì'!$E$2:$E$15</f>
+              <f>'Thanh Trì'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -1002,12 +1002,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Thanh Xuân'!$A$2:$A$15</f>
+              <f>'Thanh Xuân'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Thanh Xuân'!$B$2:$B$15</f>
+              <f>'Thanh Xuân'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -1037,12 +1037,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Thanh Xuân'!$A$2:$A$15</f>
+              <f>'Thanh Xuân'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Thanh Xuân'!$C$2:$C$15</f>
+              <f>'Thanh Xuân'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -1077,7 +1077,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Thanh Xuân'!$D$2:$D$15</f>
+              <f>'Thanh Xuân'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -1107,7 +1107,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Thanh Xuân'!$E$2:$E$15</f>
+              <f>'Thanh Xuân'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -1251,12 +1251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Tây Hồ'!$A$2:$A$15</f>
+              <f>'Tây Hồ'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tây Hồ'!$B$2:$B$15</f>
+              <f>'Tây Hồ'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -1286,12 +1286,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Tây Hồ'!$A$2:$A$15</f>
+              <f>'Tây Hồ'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tây Hồ'!$C$2:$C$15</f>
+              <f>'Tây Hồ'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -1326,7 +1326,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Tây Hồ'!$D$2:$D$15</f>
+              <f>'Tây Hồ'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -1356,7 +1356,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Tây Hồ'!$E$2:$E$15</f>
+              <f>'Tây Hồ'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -1500,12 +1500,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Đan Phượng'!$A$2:$A$15</f>
+              <f>'Đan Phượng'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Đan Phượng'!$B$2:$B$15</f>
+              <f>'Đan Phượng'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -1535,12 +1535,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Đan Phượng'!$A$2:$A$15</f>
+              <f>'Đan Phượng'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Đan Phượng'!$C$2:$C$15</f>
+              <f>'Đan Phượng'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -1575,7 +1575,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Đan Phượng'!$D$2:$D$15</f>
+              <f>'Đan Phượng'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -1605,7 +1605,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Đan Phượng'!$E$2:$E$15</f>
+              <f>'Đan Phượng'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -1749,12 +1749,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Đông Anh'!$A$2:$A$15</f>
+              <f>'Đông Anh'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Đông Anh'!$B$2:$B$15</f>
+              <f>'Đông Anh'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -1784,12 +1784,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Đông Anh'!$A$2:$A$15</f>
+              <f>'Đông Anh'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Đông Anh'!$C$2:$C$15</f>
+              <f>'Đông Anh'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -1824,7 +1824,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Đông Anh'!$D$2:$D$15</f>
+              <f>'Đông Anh'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -1854,7 +1854,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Đông Anh'!$E$2:$E$15</f>
+              <f>'Đông Anh'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -1998,12 +1998,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Đống Đa'!$A$2:$A$15</f>
+              <f>'Đống Đa'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Đống Đa'!$B$2:$B$15</f>
+              <f>'Đống Đa'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -2033,12 +2033,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Đống Đa'!$A$2:$A$15</f>
+              <f>'Đống Đa'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Đống Đa'!$C$2:$C$15</f>
+              <f>'Đống Đa'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -2073,7 +2073,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Đống Đa'!$D$2:$D$15</f>
+              <f>'Đống Đa'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -2103,7 +2103,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Đống Đa'!$E$2:$E$15</f>
+              <f>'Đống Đa'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -2247,12 +2247,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Bắc Từ Liêm'!$A$2:$A$15</f>
+              <f>'Bắc Từ Liêm'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Bắc Từ Liêm'!$B$2:$B$15</f>
+              <f>'Bắc Từ Liêm'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -2282,12 +2282,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Bắc Từ Liêm'!$A$2:$A$15</f>
+              <f>'Bắc Từ Liêm'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Bắc Từ Liêm'!$C$2:$C$15</f>
+              <f>'Bắc Từ Liêm'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -2322,7 +2322,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Bắc Từ Liêm'!$D$2:$D$15</f>
+              <f>'Bắc Từ Liêm'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -2352,7 +2352,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Bắc Từ Liêm'!$E$2:$E$15</f>
+              <f>'Bắc Từ Liêm'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -2496,12 +2496,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cầu Giấy'!$A$2:$A$15</f>
+              <f>'Cầu Giấy'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cầu Giấy'!$B$2:$B$15</f>
+              <f>'Cầu Giấy'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -2531,12 +2531,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cầu Giấy'!$A$2:$A$15</f>
+              <f>'Cầu Giấy'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cầu Giấy'!$C$2:$C$15</f>
+              <f>'Cầu Giấy'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -2571,7 +2571,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Cầu Giấy'!$D$2:$D$15</f>
+              <f>'Cầu Giấy'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -2601,7 +2601,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Cầu Giấy'!$E$2:$E$15</f>
+              <f>'Cầu Giấy'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -2745,12 +2745,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Gia Lâm'!$A$2:$A$15</f>
+              <f>'Gia Lâm'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gia Lâm'!$B$2:$B$15</f>
+              <f>'Gia Lâm'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -2780,12 +2780,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Gia Lâm'!$A$2:$A$15</f>
+              <f>'Gia Lâm'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gia Lâm'!$C$2:$C$15</f>
+              <f>'Gia Lâm'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -2820,7 +2820,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Gia Lâm'!$D$2:$D$15</f>
+              <f>'Gia Lâm'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -2850,7 +2850,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Gia Lâm'!$E$2:$E$15</f>
+              <f>'Gia Lâm'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -2994,12 +2994,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Hai Bà Trưng'!$A$2:$A$15</f>
+              <f>'Hai Bà Trưng'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Hai Bà Trưng'!$B$2:$B$15</f>
+              <f>'Hai Bà Trưng'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -3029,12 +3029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Hai Bà Trưng'!$A$2:$A$15</f>
+              <f>'Hai Bà Trưng'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Hai Bà Trưng'!$C$2:$C$15</f>
+              <f>'Hai Bà Trưng'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -3069,7 +3069,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Hai Bà Trưng'!$D$2:$D$15</f>
+              <f>'Hai Bà Trưng'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -3099,7 +3099,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Hai Bà Trưng'!$E$2:$E$15</f>
+              <f>'Hai Bà Trưng'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -3243,12 +3243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Hoài Đức'!$A$2:$A$15</f>
+              <f>'Hoài Đức'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Hoài Đức'!$B$2:$B$15</f>
+              <f>'Hoài Đức'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -3278,12 +3278,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Hoài Đức'!$A$2:$A$15</f>
+              <f>'Hoài Đức'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Hoài Đức'!$C$2:$C$15</f>
+              <f>'Hoài Đức'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -3318,7 +3318,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Hoài Đức'!$D$2:$D$15</f>
+              <f>'Hoài Đức'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -3348,7 +3348,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Hoài Đức'!$E$2:$E$15</f>
+              <f>'Hoài Đức'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -3492,12 +3492,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Hoàng Mai'!$A$2:$A$15</f>
+              <f>'Hoàng Mai'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Hoàng Mai'!$B$2:$B$15</f>
+              <f>'Hoàng Mai'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -3527,12 +3527,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Hoàng Mai'!$A$2:$A$15</f>
+              <f>'Hoàng Mai'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Hoàng Mai'!$C$2:$C$15</f>
+              <f>'Hoàng Mai'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -3567,7 +3567,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Hoàng Mai'!$D$2:$D$15</f>
+              <f>'Hoàng Mai'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -3597,7 +3597,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Hoàng Mai'!$E$2:$E$15</f>
+              <f>'Hoàng Mai'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -3741,12 +3741,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Hà Đông'!$A$2:$A$15</f>
+              <f>'Hà Đông'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Hà Đông'!$B$2:$B$15</f>
+              <f>'Hà Đông'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -3776,12 +3776,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Hà Đông'!$A$2:$A$15</f>
+              <f>'Hà Đông'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Hà Đông'!$C$2:$C$15</f>
+              <f>'Hà Đông'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -3816,7 +3816,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Hà Đông'!$D$2:$D$15</f>
+              <f>'Hà Đông'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -3846,7 +3846,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Hà Đông'!$E$2:$E$15</f>
+              <f>'Hà Đông'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -3990,12 +3990,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Long Biên'!$A$2:$A$15</f>
+              <f>'Long Biên'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Long Biên'!$B$2:$B$15</f>
+              <f>'Long Biên'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -4025,12 +4025,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Long Biên'!$A$2:$A$15</f>
+              <f>'Long Biên'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Long Biên'!$C$2:$C$15</f>
+              <f>'Long Biên'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -4065,7 +4065,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Long Biên'!$D$2:$D$15</f>
+              <f>'Long Biên'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -4095,7 +4095,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Long Biên'!$E$2:$E$15</f>
+              <f>'Long Biên'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -4197,7 +4197,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4224,7 +4224,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4251,7 +4251,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4278,7 +4278,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4305,7 +4305,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4332,7 +4332,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4359,7 +4359,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4386,7 +4386,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4413,7 +4413,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4440,7 +4440,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4467,7 +4467,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4494,7 +4494,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4521,7 +4521,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4548,7 +4548,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4575,7 +4575,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4602,7 +4602,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="5040000"/>
@@ -4912,7 +4912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1425"/>
+  <dimension ref="A1:N1441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72265,6 +72265,768 @@
         <v>44.1</v>
       </c>
     </row>
+    <row r="1426">
+      <c r="A1426" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1426" s="3" t="inlineStr">
+        <is>
+          <t>Nam Từ Liêm</t>
+        </is>
+      </c>
+      <c r="C1426" s="4" t="n">
+        <v>4694</v>
+      </c>
+      <c r="D1426" s="4" t="n">
+        <v>18776</v>
+      </c>
+      <c r="E1426" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1426" s="4" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="G1426" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1426" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="I1426" s="4" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="J1426" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="K1426" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L1426" s="4" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="M1426" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N1426" s="4" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1427" s="5" t="inlineStr">
+        <is>
+          <t>Cầu Giấy</t>
+        </is>
+      </c>
+      <c r="C1427" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1427" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1427" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1427" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1427" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1427" s="6" t="n">
+        <v>237</v>
+      </c>
+      <c r="I1427" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1427" s="6" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K1427" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1427" s="6" t="inlineStr"/>
+      <c r="M1427" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1427" s="6" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1428" s="3" t="inlineStr">
+        <is>
+          <t>Hà Đông</t>
+        </is>
+      </c>
+      <c r="C1428" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1428" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1428" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F1428" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1428" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="H1428" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="I1428" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1428" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="K1428" s="4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L1428" s="4" t="inlineStr"/>
+      <c r="M1428" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1428" s="4" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1429" s="5" t="inlineStr">
+        <is>
+          <t>Hoàng Mai</t>
+        </is>
+      </c>
+      <c r="C1429" s="6" t="n">
+        <v>3845</v>
+      </c>
+      <c r="D1429" s="6" t="n">
+        <v>24224</v>
+      </c>
+      <c r="E1429" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F1429" s="6" t="n">
+        <v>232.9</v>
+      </c>
+      <c r="G1429" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="H1429" s="6" t="n">
+        <v>735</v>
+      </c>
+      <c r="I1429" s="6" t="n">
+        <v>351</v>
+      </c>
+      <c r="J1429" s="6" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="K1429" s="6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L1429" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="M1429" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1429" s="6" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1430" s="3" t="inlineStr">
+        <is>
+          <t>Thanh Xuân</t>
+        </is>
+      </c>
+      <c r="C1430" s="4" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D1430" s="4" t="n">
+        <v>23481</v>
+      </c>
+      <c r="E1430" s="4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F1430" s="4" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="G1430" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1430" s="4" t="n">
+        <v>507</v>
+      </c>
+      <c r="I1430" s="4" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="J1430" s="4" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="K1430" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L1430" s="4" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="M1430" s="4" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="N1430" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1431" s="5" t="inlineStr">
+        <is>
+          <t>Tây Hồ</t>
+        </is>
+      </c>
+      <c r="C1431" s="6" t="n">
+        <v>2971</v>
+      </c>
+      <c r="D1431" s="6" t="n">
+        <v>16340</v>
+      </c>
+      <c r="E1431" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F1431" s="6" t="n">
+        <v>261</v>
+      </c>
+      <c r="G1431" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1431" s="6" t="n">
+        <v>401</v>
+      </c>
+      <c r="I1431" s="6" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="J1431" s="6" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="K1431" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L1431" s="6" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="M1431" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N1431" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1432" s="3" t="inlineStr">
+        <is>
+          <t>Bắc Từ Liêm</t>
+        </is>
+      </c>
+      <c r="C1432" s="4" t="n">
+        <v>2420</v>
+      </c>
+      <c r="D1432" s="4" t="n">
+        <v>16698</v>
+      </c>
+      <c r="E1432" s="4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F1432" s="4" t="n">
+        <v>122.8</v>
+      </c>
+      <c r="G1432" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1432" s="4" t="n">
+        <v>456</v>
+      </c>
+      <c r="I1432" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="J1432" s="4" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="K1432" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L1432" s="4" t="n">
+        <v>-33.6</v>
+      </c>
+      <c r="M1432" s="4" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="N1432" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1433" s="5" t="inlineStr">
+        <is>
+          <t>Gia Lâm</t>
+        </is>
+      </c>
+      <c r="C1433" s="6" t="n">
+        <v>2058</v>
+      </c>
+      <c r="D1433" s="6" t="n">
+        <v>10290</v>
+      </c>
+      <c r="E1433" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1433" s="6" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="G1433" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1433" s="6" t="n">
+        <v>358</v>
+      </c>
+      <c r="I1433" s="6" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="J1433" s="6" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="K1433" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1433" s="6" t="n">
+        <v>-29.3</v>
+      </c>
+      <c r="M1433" s="6" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="N1433" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1434" s="3" t="inlineStr">
+        <is>
+          <t>Long Biên</t>
+        </is>
+      </c>
+      <c r="C1434" s="4" t="n">
+        <v>3858</v>
+      </c>
+      <c r="D1434" s="4" t="n">
+        <v>37808</v>
+      </c>
+      <c r="E1434" s="4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F1434" s="4" t="n">
+        <v>250.7</v>
+      </c>
+      <c r="G1434" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="H1434" s="4" t="n">
+        <v>828</v>
+      </c>
+      <c r="I1434" s="4" t="n">
+        <v>483.9</v>
+      </c>
+      <c r="J1434" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K1434" s="4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L1434" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="M1434" s="4" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="N1434" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1435" s="5" t="inlineStr">
+        <is>
+          <t>Hoài Đức</t>
+        </is>
+      </c>
+      <c r="C1435" s="6" t="n">
+        <v>2618</v>
+      </c>
+      <c r="D1435" s="6" t="n">
+        <v>16755</v>
+      </c>
+      <c r="E1435" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F1435" s="6" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="G1435" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="H1435" s="6" t="n">
+        <v>579</v>
+      </c>
+      <c r="I1435" s="6" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="J1435" s="6" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="K1435" s="6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L1435" s="6" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="M1435" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1435" s="6" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1436" s="3" t="inlineStr">
+        <is>
+          <t>Đống Đa</t>
+        </is>
+      </c>
+      <c r="C1436" s="4" t="n">
+        <v>3179</v>
+      </c>
+      <c r="D1436" s="4" t="n">
+        <v>32744</v>
+      </c>
+      <c r="E1436" s="4" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F1436" s="4" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="G1436" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1436" s="4" t="n">
+        <v>704</v>
+      </c>
+      <c r="I1436" s="4" t="n">
+        <v>352</v>
+      </c>
+      <c r="J1436" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K1436" s="4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L1436" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="M1436" s="4" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="N1436" s="4" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1437" s="5" t="inlineStr">
+        <is>
+          <t>Hai Bà Trưng</t>
+        </is>
+      </c>
+      <c r="C1437" s="6" t="n">
+        <v>2266</v>
+      </c>
+      <c r="D1437" s="6" t="n">
+        <v>23793</v>
+      </c>
+      <c r="E1437" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1437" s="6" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="G1437" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1437" s="6" t="n">
+        <v>606</v>
+      </c>
+      <c r="I1437" s="6" t="n">
+        <v>257</v>
+      </c>
+      <c r="J1437" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="K1437" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L1437" s="6" t="n">
+        <v>-17</v>
+      </c>
+      <c r="M1437" s="6" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="N1437" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1438" s="3" t="inlineStr">
+        <is>
+          <t>Thanh Trì</t>
+        </is>
+      </c>
+      <c r="C1438" s="4" t="n">
+        <v>1214</v>
+      </c>
+      <c r="D1438" s="4" t="n">
+        <v>11776</v>
+      </c>
+      <c r="E1438" s="4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F1438" s="4" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="G1438" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H1438" s="4" t="n">
+        <v>609</v>
+      </c>
+      <c r="I1438" s="4" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="J1438" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="K1438" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L1438" s="4" t="n">
+        <v>-29.2</v>
+      </c>
+      <c r="M1438" s="4" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="N1438" s="4" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1439" s="5" t="inlineStr">
+        <is>
+          <t>Ba Đình</t>
+        </is>
+      </c>
+      <c r="C1439" s="6" t="n">
+        <v>2165</v>
+      </c>
+      <c r="D1439" s="6" t="n">
+        <v>23815</v>
+      </c>
+      <c r="E1439" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1439" s="6" t="n">
+        <v>238.3</v>
+      </c>
+      <c r="G1439" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1439" s="6" t="n">
+        <v>620</v>
+      </c>
+      <c r="I1439" s="6" t="n">
+        <v>252.4</v>
+      </c>
+      <c r="J1439" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="K1439" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L1439" s="6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="M1439" s="6" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="N1439" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1440" s="3" t="inlineStr">
+        <is>
+          <t>Đông Anh</t>
+        </is>
+      </c>
+      <c r="C1440" s="4" t="n">
+        <v>1867</v>
+      </c>
+      <c r="D1440" s="4" t="n">
+        <v>19043</v>
+      </c>
+      <c r="E1440" s="4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F1440" s="4" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="G1440" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="H1440" s="4" t="n">
+        <v>695</v>
+      </c>
+      <c r="I1440" s="4" t="n">
+        <v>252.3</v>
+      </c>
+      <c r="J1440" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="K1440" s="4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="L1440" s="4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M1440" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N1440" s="4" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1441" s="5" t="inlineStr">
+        <is>
+          <t>Đan Phượng</t>
+        </is>
+      </c>
+      <c r="C1441" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1441" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1441" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F1441" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1441" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="H1441" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="I1441" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1441" s="6" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="K1441" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L1441" s="6" t="inlineStr"/>
+      <c r="M1441" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1441" s="6" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -72276,7 +73038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72577,6 +73339,25 @@
       </c>
       <c r="E15" t="n">
         <v>91</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3858</v>
+      </c>
+      <c r="C16" t="n">
+        <v>37808</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E16" t="n">
+        <v>250.7</v>
       </c>
     </row>
   </sheetData>
@@ -72591,7 +73372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72892,6 +73673,25 @@
       </c>
       <c r="E15" t="n">
         <v>88.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4694</v>
+      </c>
+      <c r="C16" t="n">
+        <v>18776</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>133.8</v>
       </c>
     </row>
   </sheetData>
@@ -72906,7 +73706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -73207,6 +74007,25 @@
       </c>
       <c r="E15" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1214</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11776</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E16" t="n">
+        <v>130.9</v>
       </c>
     </row>
   </sheetData>
@@ -73221,7 +74040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -73522,6 +74341,25 @@
       </c>
       <c r="E15" t="n">
         <v>98.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3403</v>
+      </c>
+      <c r="C16" t="n">
+        <v>23481</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>161.6</v>
       </c>
     </row>
   </sheetData>
@@ -73536,7 +74374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -73837,6 +74675,25 @@
       </c>
       <c r="E15" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2971</v>
+      </c>
+      <c r="C16" t="n">
+        <v>16340</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -73851,7 +74708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -74152,6 +75009,25 @@
       </c>
       <c r="E15" t="n">
         <v>68.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -74166,7 +75042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -74467,6 +75343,25 @@
       </c>
       <c r="E15" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1867</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19043</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>203.7</v>
       </c>
     </row>
   </sheetData>
@@ -74481,7 +75376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -74782,6 +75677,25 @@
       </c>
       <c r="E15" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3179</v>
+      </c>
+      <c r="C16" t="n">
+        <v>32744</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>237.6</v>
       </c>
     </row>
   </sheetData>
@@ -74796,7 +75710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -75097,6 +76011,25 @@
       </c>
       <c r="E15" t="n">
         <v>130.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C16" t="n">
+        <v>23815</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>238.3</v>
       </c>
     </row>
   </sheetData>
@@ -75111,7 +76044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -75412,6 +76345,25 @@
       </c>
       <c r="E15" t="n">
         <v>98.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2420</v>
+      </c>
+      <c r="C16" t="n">
+        <v>16698</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>122.8</v>
       </c>
     </row>
   </sheetData>
@@ -75426,7 +76378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -75727,6 +76679,25 @@
       </c>
       <c r="E15" t="n">
         <v>111.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -75741,7 +76712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -76042,6 +77013,25 @@
       </c>
       <c r="E15" t="n">
         <v>72.90000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2058</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10290</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>130.7</v>
       </c>
     </row>
   </sheetData>
@@ -76056,7 +77046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -76357,6 +77347,25 @@
       </c>
       <c r="E15" t="n">
         <v>97.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2266</v>
+      </c>
+      <c r="C16" t="n">
+        <v>23793</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>153.5</v>
       </c>
     </row>
   </sheetData>
@@ -76371,7 +77380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -76672,6 +77681,25 @@
       </c>
       <c r="E15" t="n">
         <v>81.59999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2618</v>
+      </c>
+      <c r="C16" t="n">
+        <v>16755</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>146.2</v>
       </c>
     </row>
   </sheetData>
@@ -76686,7 +77714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -76987,6 +78015,25 @@
       </c>
       <c r="E15" t="n">
         <v>88.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3845</v>
+      </c>
+      <c r="C16" t="n">
+        <v>24224</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>232.9</v>
       </c>
     </row>
   </sheetData>
@@ -77001,7 +78048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -77304,6 +78351,25 @@
         <v>81.90000000000001</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/CHI_SO_PHAI_SINH.xlsx
+++ b/data/CHI_SO_PHAI_SINH.xlsx
@@ -4912,7 +4912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1441"/>
+  <dimension ref="A1:N1457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -73024,6 +73024,774 @@
         <v>0</v>
       </c>
       <c r="N1441" s="6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1442" s="3" t="inlineStr">
+        <is>
+          <t>Nam Từ Liêm</t>
+        </is>
+      </c>
+      <c r="C1442" s="4" t="n">
+        <v>4915</v>
+      </c>
+      <c r="D1442" s="4" t="n">
+        <v>18677</v>
+      </c>
+      <c r="E1442" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F1442" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1442" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1442" s="4" t="n">
+        <v>376</v>
+      </c>
+      <c r="I1442" s="4" t="n">
+        <v>210.1</v>
+      </c>
+      <c r="J1442" s="4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="K1442" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L1442" s="4" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M1442" s="4" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="N1442" s="4" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1443" s="5" t="inlineStr">
+        <is>
+          <t>Cầu Giấy</t>
+        </is>
+      </c>
+      <c r="C1443" s="6" t="n">
+        <v>4909</v>
+      </c>
+      <c r="D1443" s="6" t="n">
+        <v>30927</v>
+      </c>
+      <c r="E1443" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F1443" s="6" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="G1443" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1443" s="6" t="n">
+        <v>567</v>
+      </c>
+      <c r="I1443" s="6" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="J1443" s="6" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="K1443" s="6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L1443" s="6" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="M1443" s="6" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="N1443" s="6" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1444" s="3" t="inlineStr">
+        <is>
+          <t>Hà Đông</t>
+        </is>
+      </c>
+      <c r="C1444" s="4" t="n">
+        <v>5774</v>
+      </c>
+      <c r="D1444" s="4" t="n">
+        <v>34067</v>
+      </c>
+      <c r="E1444" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F1444" s="4" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="G1444" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1444" s="4" t="n">
+        <v>642</v>
+      </c>
+      <c r="I1444" s="4" t="n">
+        <v>403</v>
+      </c>
+      <c r="J1444" s="4" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="K1444" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L1444" s="4" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="M1444" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N1444" s="4" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1445" s="5" t="inlineStr">
+        <is>
+          <t>Hoàng Mai</t>
+        </is>
+      </c>
+      <c r="C1445" s="6" t="n">
+        <v>3867</v>
+      </c>
+      <c r="D1445" s="6" t="n">
+        <v>23975</v>
+      </c>
+      <c r="E1445" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F1445" s="6" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="G1445" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="H1445" s="6" t="n">
+        <v>712</v>
+      </c>
+      <c r="I1445" s="6" t="n">
+        <v>347.4</v>
+      </c>
+      <c r="J1445" s="6" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="K1445" s="6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L1445" s="6" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="M1445" s="6" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="N1445" s="6" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1446" s="3" t="inlineStr">
+        <is>
+          <t>Thanh Xuân</t>
+        </is>
+      </c>
+      <c r="C1446" s="4" t="n">
+        <v>3388</v>
+      </c>
+      <c r="D1446" s="4" t="n">
+        <v>24055</v>
+      </c>
+      <c r="E1446" s="4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F1446" s="4" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="G1446" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1446" s="4" t="n">
+        <v>561</v>
+      </c>
+      <c r="I1446" s="4" t="n">
+        <v>264.6</v>
+      </c>
+      <c r="J1446" s="4" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="K1446" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L1446" s="4" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="M1446" s="4" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N1446" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1447" s="5" t="inlineStr">
+        <is>
+          <t>Tây Hồ</t>
+        </is>
+      </c>
+      <c r="C1447" s="6" t="n">
+        <v>3093</v>
+      </c>
+      <c r="D1447" s="6" t="n">
+        <v>16702</v>
+      </c>
+      <c r="E1447" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F1447" s="6" t="n">
+        <v>202.8</v>
+      </c>
+      <c r="G1447" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1447" s="6" t="n">
+        <v>418</v>
+      </c>
+      <c r="I1447" s="6" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="J1447" s="6" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="K1447" s="6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L1447" s="6" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="M1447" s="6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N1447" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1448" s="3" t="inlineStr">
+        <is>
+          <t>Bắc Từ Liêm</t>
+        </is>
+      </c>
+      <c r="C1448" s="4" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D1448" s="4" t="n">
+        <v>17430</v>
+      </c>
+      <c r="E1448" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1448" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="G1448" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1448" s="4" t="n">
+        <v>484</v>
+      </c>
+      <c r="I1448" s="4" t="n">
+        <v>200.4</v>
+      </c>
+      <c r="J1448" s="4" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="K1448" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L1448" s="4" t="n">
+        <v>-32</v>
+      </c>
+      <c r="M1448" s="4" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="N1448" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1449" s="5" t="inlineStr">
+        <is>
+          <t>Gia Lâm</t>
+        </is>
+      </c>
+      <c r="C1449" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D1449" s="6" t="n">
+        <v>8782</v>
+      </c>
+      <c r="E1449" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F1449" s="6" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="G1449" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="H1449" s="6" t="n">
+        <v>303</v>
+      </c>
+      <c r="I1449" s="6" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="J1449" s="6" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="K1449" s="6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L1449" s="6" t="n">
+        <v>-50.6</v>
+      </c>
+      <c r="M1449" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="N1449" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1450" s="3" t="inlineStr">
+        <is>
+          <t>Long Biên</t>
+        </is>
+      </c>
+      <c r="C1450" s="4" t="n">
+        <v>4044</v>
+      </c>
+      <c r="D1450" s="4" t="n">
+        <v>34778</v>
+      </c>
+      <c r="E1450" s="4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F1450" s="4" t="n">
+        <v>195.2</v>
+      </c>
+      <c r="G1450" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="H1450" s="4" t="n">
+        <v>790</v>
+      </c>
+      <c r="I1450" s="4" t="n">
+        <v>445.2</v>
+      </c>
+      <c r="J1450" s="4" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="K1450" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L1450" s="4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="M1450" s="4" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="N1450" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1451" s="5" t="inlineStr">
+        <is>
+          <t>Hoài Đức</t>
+        </is>
+      </c>
+      <c r="C1451" s="6" t="n">
+        <v>2418</v>
+      </c>
+      <c r="D1451" s="6" t="n">
+        <v>15233</v>
+      </c>
+      <c r="E1451" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F1451" s="6" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G1451" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="H1451" s="6" t="n">
+        <v>531</v>
+      </c>
+      <c r="I1451" s="6" t="n">
+        <v>204.1</v>
+      </c>
+      <c r="J1451" s="6" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="K1451" s="6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L1451" s="6" t="n">
+        <v>-45.2</v>
+      </c>
+      <c r="M1451" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N1451" s="6" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1452" s="3" t="inlineStr">
+        <is>
+          <t>Đống Đa</t>
+        </is>
+      </c>
+      <c r="C1452" s="4" t="n">
+        <v>3288</v>
+      </c>
+      <c r="D1452" s="4" t="n">
+        <v>32880</v>
+      </c>
+      <c r="E1452" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1452" s="4" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="G1452" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1452" s="4" t="n">
+        <v>693</v>
+      </c>
+      <c r="I1452" s="4" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="J1452" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K1452" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1452" s="4" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="M1452" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N1452" s="4" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1453" s="5" t="inlineStr">
+        <is>
+          <t>Hai Bà Trưng</t>
+        </is>
+      </c>
+      <c r="C1453" s="6" t="n">
+        <v>2226</v>
+      </c>
+      <c r="D1453" s="6" t="n">
+        <v>22928</v>
+      </c>
+      <c r="E1453" s="6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F1453" s="6" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="G1453" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1453" s="6" t="n">
+        <v>593</v>
+      </c>
+      <c r="I1453" s="6" t="n">
+        <v>247.6</v>
+      </c>
+      <c r="J1453" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="K1453" s="6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L1453" s="6" t="n">
+        <v>-18</v>
+      </c>
+      <c r="M1453" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="N1453" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1454" s="3" t="inlineStr">
+        <is>
+          <t>Thanh Trì</t>
+        </is>
+      </c>
+      <c r="C1454" s="4" t="n">
+        <v>1074</v>
+      </c>
+      <c r="D1454" s="4" t="n">
+        <v>10310</v>
+      </c>
+      <c r="E1454" s="4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F1454" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="G1454" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1454" s="4" t="n">
+        <v>610</v>
+      </c>
+      <c r="I1454" s="4" t="n">
+        <v>148.6</v>
+      </c>
+      <c r="J1454" s="4" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K1454" s="4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L1454" s="4" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="M1454" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N1454" s="4" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1455" s="5" t="inlineStr">
+        <is>
+          <t>Ba Đình</t>
+        </is>
+      </c>
+      <c r="C1455" s="6" t="n">
+        <v>2096</v>
+      </c>
+      <c r="D1455" s="6" t="n">
+        <v>19912</v>
+      </c>
+      <c r="E1455" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F1455" s="6" t="n">
+        <v>226.4</v>
+      </c>
+      <c r="G1455" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1455" s="6" t="n">
+        <v>530</v>
+      </c>
+      <c r="I1455" s="6" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="J1455" s="6" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="K1455" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L1455" s="6" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="M1455" s="6" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="N1455" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1456" s="3" t="inlineStr">
+        <is>
+          <t>Đông Anh</t>
+        </is>
+      </c>
+      <c r="C1456" s="4" t="n">
+        <v>1760</v>
+      </c>
+      <c r="D1456" s="4" t="n">
+        <v>17248</v>
+      </c>
+      <c r="E1456" s="4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F1456" s="4" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="G1456" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H1456" s="4" t="n">
+        <v>653</v>
+      </c>
+      <c r="I1456" s="4" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="J1456" s="4" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="K1456" s="4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L1456" s="4" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M1456" s="4" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="N1456" s="4" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1457" s="5" t="inlineStr">
+        <is>
+          <t>Đan Phượng</t>
+        </is>
+      </c>
+      <c r="C1457" s="6" t="n">
+        <v>721</v>
+      </c>
+      <c r="D1457" s="6" t="n">
+        <v>2668</v>
+      </c>
+      <c r="E1457" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F1457" s="6" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="G1457" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1457" s="6" t="n">
+        <v>307</v>
+      </c>
+      <c r="I1457" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J1457" s="6" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="K1457" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L1457" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M1457" s="6" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="N1457" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -73348,16 +74116,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3858</v>
+        <v>4044</v>
       </c>
       <c r="C16" t="n">
-        <v>37808</v>
+        <v>34778</v>
       </c>
       <c r="D16" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="E16" t="n">
-        <v>250.7</v>
+        <v>195.2</v>
       </c>
     </row>
   </sheetData>
@@ -73682,16 +74450,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4694</v>
+        <v>4915</v>
       </c>
       <c r="C16" t="n">
-        <v>18776</v>
+        <v>18677</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="E16" t="n">
-        <v>133.8</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -74016,16 +74784,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1214</v>
+        <v>1074</v>
       </c>
       <c r="C16" t="n">
-        <v>11776</v>
+        <v>10310</v>
       </c>
       <c r="D16" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E16" t="n">
-        <v>130.9</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -74350,16 +75118,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3403</v>
+        <v>3388</v>
       </c>
       <c r="C16" t="n">
-        <v>23481</v>
+        <v>24055</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="E16" t="n">
-        <v>161.6</v>
+        <v>120.4</v>
       </c>
     </row>
   </sheetData>
@@ -74684,16 +75452,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2971</v>
+        <v>3093</v>
       </c>
       <c r="C16" t="n">
-        <v>16340</v>
+        <v>16702</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="E16" t="n">
-        <v>261</v>
+        <v>202.8</v>
       </c>
     </row>
   </sheetData>
@@ -75018,16 +75786,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>721</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2668</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>160.2</v>
       </c>
     </row>
   </sheetData>
@@ -75352,16 +76120,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1867</v>
+        <v>1760</v>
       </c>
       <c r="C16" t="n">
-        <v>19043</v>
+        <v>17248</v>
       </c>
       <c r="D16" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>203.7</v>
+        <v>166.7</v>
       </c>
     </row>
   </sheetData>
@@ -75686,16 +76454,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3179</v>
+        <v>3288</v>
       </c>
       <c r="C16" t="n">
-        <v>32744</v>
+        <v>32880</v>
       </c>
       <c r="D16" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>237.6</v>
+        <v>262.5</v>
       </c>
     </row>
   </sheetData>
@@ -76020,16 +76788,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2165</v>
+        <v>2096</v>
       </c>
       <c r="C16" t="n">
-        <v>23815</v>
+        <v>19912</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="E16" t="n">
-        <v>238.3</v>
+        <v>226.4</v>
       </c>
     </row>
   </sheetData>
@@ -76354,16 +77122,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2420</v>
+        <v>2490</v>
       </c>
       <c r="C16" t="n">
-        <v>16698</v>
+        <v>17430</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>122.8</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -76688,16 +77456,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>4909</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>30927</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>135.4</v>
       </c>
     </row>
   </sheetData>
@@ -77022,16 +77790,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2058</v>
+        <v>2142</v>
       </c>
       <c r="C16" t="n">
-        <v>10290</v>
+        <v>8782</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="E16" t="n">
-        <v>130.7</v>
+        <v>73.3</v>
       </c>
     </row>
   </sheetData>
@@ -77356,16 +78124,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2266</v>
+        <v>2226</v>
       </c>
       <c r="C16" t="n">
-        <v>23793</v>
+        <v>22928</v>
       </c>
       <c r="D16" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="E16" t="n">
-        <v>153.5</v>
+        <v>121.8</v>
       </c>
     </row>
   </sheetData>
@@ -77690,16 +78458,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2618</v>
+        <v>2418</v>
       </c>
       <c r="C16" t="n">
-        <v>16755</v>
+        <v>15233</v>
       </c>
       <c r="D16" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="E16" t="n">
-        <v>146.2</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -78024,16 +78792,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3845</v>
+        <v>3867</v>
       </c>
       <c r="C16" t="n">
-        <v>24224</v>
+        <v>23975</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="E16" t="n">
-        <v>232.9</v>
+        <v>102.7</v>
       </c>
     </row>
   </sheetData>
@@ -78358,16 +79126,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>5774</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>34067</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>118.5</v>
       </c>
     </row>
   </sheetData>
